--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486280_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486280_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. MOTOS CABODEVILLA</t>
+          <t>M. ANSORREGUI DEBA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3212</v>
+        <v>2.3601</v>
       </c>
       <c r="E2" t="n">
-        <v>4.052</v>
+        <v>2.4968</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7308</v>
+        <v>-0.1367</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0672</v>
+        <v>0.1615</v>
       </c>
       <c r="H2" t="n">
-        <v>2.6458</v>
+        <v>-2.6976</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.5786</v>
+        <v>2.8591</v>
       </c>
       <c r="J2" t="n">
-        <v>1.8253</v>
+        <v>1.1697</v>
       </c>
       <c r="K2" t="n">
-        <v>2.3026</v>
+        <v>-2.5787</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.4773</v>
+        <v>3.7484</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.7581</v>
+        <v>-1.0082</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3433</v>
+        <v>-0.1188</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.1013</v>
+        <v>-0.8893</v>
       </c>
       <c r="P2" t="n">
-        <v>0.435</v>
+        <v>0.2175</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6525</v>
+        <v>0.2175</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2095</v>
+        <v>0.8511</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4443</v>
+        <v>0.1971</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7652</v>
+        <v>0.654</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.3904</v>
+        <v>1.13</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.3904</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. ANSORREGUI DEBA</t>
+          <t>A. ZUBIZARRETA ARANBARRI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5005</v>
+        <v>2.1923</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3598</v>
+        <v>3.5267</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1408</v>
+        <v>-1.3343</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1615</v>
+        <v>1.1741</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.6976</v>
+        <v>0.6203</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8591</v>
+        <v>0.5538</v>
       </c>
       <c r="J3" t="n">
-        <v>1.1697</v>
+        <v>3.1249</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.5787</v>
+        <v>0.6387</v>
       </c>
       <c r="L3" t="n">
-        <v>3.7484</v>
+        <v>2.4862</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.0082</v>
+        <v>-1.9508</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1188</v>
+        <v>-0.0184</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8893</v>
+        <v>-1.9324</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2175</v>
+        <v>-0.87</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R3" t="n">
         <v>0.2175</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9915</v>
+        <v>0.7583</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0601</v>
+        <v>0.3593</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9314</v>
+        <v>0.399</v>
       </c>
       <c r="V3" t="n">
         <v>1.13</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. ZUBIZARRETA ARANBARRI</t>
+          <t>M. MOTOS CABODEVILLA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0575</v>
+        <v>2.0393</v>
       </c>
       <c r="E4" t="n">
-        <v>3.6384</v>
+        <v>3.1399</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.5809</v>
+        <v>-1.1007</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1741</v>
+        <v>0.0672</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6203</v>
+        <v>2.6458</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5538</v>
+        <v>-2.5786</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1249</v>
+        <v>1.8253</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6387</v>
+        <v>2.3026</v>
       </c>
       <c r="L4" t="n">
-        <v>2.4862</v>
+        <v>-0.4773</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.9508</v>
+        <v>-1.7581</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0184</v>
+        <v>0.3433</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.9324</v>
+        <v>-2.1013</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.87</v>
+        <v>0.435</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0875</v>
+        <v>-0.2175</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2175</v>
+        <v>0.6525</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6234</v>
+        <v>1.9275</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4711</v>
+        <v>1.5322</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1524</v>
+        <v>0.3953</v>
       </c>
       <c r="V4" t="n">
-        <v>1.13</v>
+        <v>-0.3904</v>
       </c>
       <c r="W4" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.457</v>
+        <v>1.4956</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8017</v>
+        <v>2.0252</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3447</v>
+        <v>-0.5296</v>
       </c>
       <c r="G5" t="n">
         <v>1.2618</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1952</v>
+        <v>0.2337</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.399</v>
+        <v>-0.1754</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5941</v>
+        <v>0.4092</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8397</v>
+        <v>1.1869</v>
       </c>
       <c r="E6" t="n">
-        <v>2.703</v>
+        <v>2.8653</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.8633</v>
+        <v>-1.6784</v>
       </c>
       <c r="G6" t="n">
         <v>5.0813</v>
@@ -922,13 +922,13 @@
         <v>0.6525</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2603</v>
+        <v>0.6075</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5997</v>
+        <v>0.7619</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3394</v>
+        <v>-0.1544</v>
       </c>
       <c r="V6" t="n">
         <v>-1.6743</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. NGOM</t>
+          <t>O. HANZLIK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2604</v>
+        <v>0.2938</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8738</v>
+        <v>0.0429</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1342</v>
+        <v>0.2508</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.4266</v>
+        <v>-0.1031</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.7181</v>
+        <v>0.7814</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7084</v>
+        <v>-0.8845</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2598</v>
+        <v>-0.3404</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.4838</v>
+        <v>0.4197</v>
       </c>
       <c r="L7" t="n">
-        <v>1.224</v>
+        <v>-0.7601</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.1668</v>
+        <v>0.2373</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2344</v>
+        <v>0.3617</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.9324</v>
+        <v>-0.1243</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.87</v>
+        <v>0.2175</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0875</v>
+        <v>-0.2175</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2175</v>
+        <v>0.435</v>
       </c>
       <c r="S7" t="n">
-        <v>2.1014</v>
+        <v>0.1794</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0911</v>
+        <v>0.6009</v>
       </c>
       <c r="U7" t="n">
-        <v>1.0103</v>
+        <v>-0.4215</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9347</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O. HANZLIK</t>
+          <t>G. KORSANTIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.586</v>
+        <v>-1.1003</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4978</v>
+        <v>0.5219</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0882</v>
+        <v>-1.6223</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1031</v>
+        <v>-0.4197</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7814</v>
+        <v>1.688</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8845</v>
+        <v>-2.1077</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3404</v>
+        <v>0.504</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4197</v>
+        <v>1.2108</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7601</v>
+        <v>-0.7068</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2373</v>
+        <v>-0.9237</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3617</v>
+        <v>0.4772</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1243</v>
+        <v>-1.4009</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2175</v>
+        <v>-1.9576</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2175</v>
+        <v>-2.3926</v>
       </c>
       <c r="R8" t="n">
         <v>0.435</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7005</v>
+        <v>0.5167</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0601</v>
+        <v>0.5203</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7606000000000001</v>
+        <v>-0.0036</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.7602</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.8902</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2339</v>
+        <v>-1.1723</v>
       </c>
       <c r="E9" t="n">
         <v>-0.8255</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4084</v>
+        <v>-0.3467</v>
       </c>
       <c r="G9" t="n">
         <v>-0.84</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3939</v>
+        <v>-0.3323</v>
       </c>
       <c r="T9" t="n">
         <v>-0.137</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2569</v>
+        <v>-0.1953</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. KORSANTIA</t>
+          <t>A. NGOM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0196</v>
+        <v>-1.3317</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3974</v>
+        <v>0.2032</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6223</v>
+        <v>-1.5349</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4197</v>
+        <v>-2.4266</v>
       </c>
       <c r="H10" t="n">
-        <v>1.688</v>
+        <v>-1.7181</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.1077</v>
+        <v>-0.7084</v>
       </c>
       <c r="J10" t="n">
-        <v>0.504</v>
+        <v>-0.2598</v>
       </c>
       <c r="K10" t="n">
-        <v>1.2108</v>
+        <v>-1.4838</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7068</v>
+        <v>1.224</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9237</v>
+        <v>-2.1668</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4772</v>
+        <v>-0.2344</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.4009</v>
+        <v>-1.9324</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.9576</v>
+        <v>-0.87</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.3926</v>
+        <v>-1.0875</v>
       </c>
       <c r="R10" t="n">
-        <v>0.435</v>
+        <v>0.2175</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4026</v>
+        <v>1.0302</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.399</v>
+        <v>0.4206</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0036</v>
+        <v>0.6096</v>
       </c>
       <c r="V10" t="n">
-        <v>0.7602</v>
+        <v>0.9347</v>
       </c>
       <c r="W10" t="n">
-        <v>1.8902</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.13</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3708</v>
+        <v>-1.3591</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2546</v>
+        <v>0.6647</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.1162</v>
+        <v>-2.0238</v>
       </c>
       <c r="G11" t="n">
         <v>0.5268</v>
@@ -1312,13 +1312,13 @@
         <v>0.87</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8324</v>
+        <v>0.1794</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0274</v>
+        <v>-0.1081</v>
       </c>
       <c r="U11" t="n">
-        <v>0.195</v>
+        <v>0.2875</v>
       </c>
       <c r="V11" t="n">
         <v>-0.7602</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.215</v>
+        <v>-2.7446</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2522</v>
+        <v>-0.09</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.9628</v>
+        <v>-2.6546</v>
       </c>
       <c r="G12" t="n">
         <v>0.8794999999999999</v>
@@ -1390,13 +1390,13 @@
         <v>0.6525</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.137</v>
+        <v>0.3335</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4747</v>
+        <v>0.6369</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6117</v>
+        <v>-0.3034</v>
       </c>
       <c r="V12" t="n">
         <v>-1.13</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4901999999999989</v>
+        <v>1.860000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>13.2012</v>
+        <v>14.5711</v>
       </c>
       <c r="F13" t="n">
-        <v>-12.711</v>
+        <v>-12.7112</v>
       </c>
       <c r="G13" t="n">
-        <v>5.3628</v>
+        <v>5.362799999999999</v>
       </c>
       <c r="H13" t="n">
         <v>9.610200000000001</v>
@@ -1447,7 +1447,7 @@
         <v>8.1533</v>
       </c>
       <c r="L13" t="n">
-        <v>7.626100000000001</v>
+        <v>7.6261</v>
       </c>
       <c r="M13" t="n">
         <v>-10.4166</v>
@@ -1465,19 +1465,19 @@
         <v>-14.1379</v>
       </c>
       <c r="R13" t="n">
-        <v>4.350000000000001</v>
+        <v>4.35</v>
       </c>
       <c r="S13" t="n">
-        <v>4.914899999999999</v>
+        <v>6.285</v>
       </c>
       <c r="T13" t="n">
-        <v>3.238699999999999</v>
+        <v>4.608700000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>1.6762</v>
+        <v>1.6764</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-2.220446049250313e-16</v>
       </c>
       <c r="W13" t="n">
         <v>8.321099999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.0324</v>
+        <v>6.4216</v>
       </c>
       <c r="E14" t="n">
-        <v>8.451599999999999</v>
+        <v>8.5634</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.4192</v>
+        <v>-2.1418</v>
       </c>
       <c r="G14" t="n">
         <v>3.279</v>
@@ -1546,13 +1546,13 @@
         <v>1.305</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.637</v>
+        <v>-0.2478</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0517</v>
+        <v>0.1634</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6887</v>
+        <v>-0.4113</v>
       </c>
       <c r="V14" t="n">
         <v>2.0854</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.3038</v>
+        <v>5.4098</v>
       </c>
       <c r="E15" t="n">
-        <v>5.9809</v>
+        <v>7.2102</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.6771</v>
+        <v>-1.8004</v>
       </c>
       <c r="G15" t="n">
         <v>3.5286</v>
@@ -1624,13 +1624,13 @@
         <v>1.9576</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.7898</v>
+        <v>-0.6838</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.3699</v>
+        <v>-0.1406</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4199</v>
+        <v>-0.5432</v>
       </c>
       <c r="V15" t="n">
         <v>1.695</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1048</v>
+        <v>1.5832</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2024</v>
+        <v>1.5318</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.09760000000000001</v>
+        <v>0.0514</v>
       </c>
       <c r="G16" t="n">
         <v>1.0839</v>
@@ -1702,13 +1702,13 @@
         <v>0.87</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3461</v>
+        <v>-0.1754</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5997</v>
+        <v>-0.0709</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2536</v>
+        <v>-0.1046</v>
       </c>
       <c r="V16" t="n">
         <v>-0.1952</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. DOS ANJOS DE PAULA</t>
+          <t>D. DE SOUSA ANJO BRITO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.096</v>
+        <v>1.4403</v>
       </c>
       <c r="E17" t="n">
-        <v>4.4856</v>
+        <v>1.4178</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.3896</v>
+        <v>0.0225</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3531</v>
+        <v>0.4807</v>
       </c>
       <c r="H17" t="n">
-        <v>0.043</v>
+        <v>-1.4174</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3961</v>
+        <v>1.8981</v>
       </c>
       <c r="J17" t="n">
-        <v>1.7835</v>
+        <v>2.1965</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4393</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3442</v>
+        <v>2.8321</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.1366</v>
+        <v>-1.7158</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3963</v>
+        <v>-0.7819</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7403</v>
+        <v>-0.9339</v>
       </c>
       <c r="P17" t="n">
-        <v>0.87</v>
+        <v>1.7401</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9576</v>
+        <v>1.7401</v>
       </c>
       <c r="S17" t="n">
-        <v>1.1886</v>
+        <v>-0.7805</v>
       </c>
       <c r="T17" t="n">
-        <v>1.1392</v>
+        <v>-0.7786999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0494</v>
+        <v>-0.0018</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3904</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.6504</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.2599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. DE SOUSA ANJO BRITO</t>
+          <t>F. DOS ANJOS DE PAULA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1179</v>
+        <v>0.8128</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3061</v>
+        <v>3.4798</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1882</v>
+        <v>-2.667</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4807</v>
+        <v>-0.3531</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.4174</v>
+        <v>0.043</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8981</v>
+        <v>-0.3961</v>
       </c>
       <c r="J18" t="n">
-        <v>2.1965</v>
+        <v>1.7835</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6356000000000001</v>
+        <v>1.4393</v>
       </c>
       <c r="L18" t="n">
-        <v>2.8321</v>
+        <v>0.3442</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.7158</v>
+        <v>-2.1366</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7819</v>
+        <v>-1.3963</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9339</v>
+        <v>-0.7403</v>
       </c>
       <c r="P18" t="n">
-        <v>1.7401</v>
+        <v>0.87</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7401</v>
+        <v>1.9576</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1029</v>
+        <v>-0.0946</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8904</v>
+        <v>0.1334</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2125</v>
+        <v>-0.228</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.3904</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.6504</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. ANDERSSON</t>
+          <t>A. GRELA ROJAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7235</v>
+        <v>-0.7832</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4387</v>
+        <v>-1.0186</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.1622</v>
+        <v>0.2354</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.65</v>
+        <v>0.8532999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4564</v>
+        <v>-0.7452</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1936</v>
+        <v>1.5985</v>
       </c>
       <c r="J19" t="n">
-        <v>2.2691</v>
+        <v>0.5737</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2769</v>
+        <v>-0.7268</v>
       </c>
       <c r="L19" t="n">
-        <v>1.9922</v>
+        <v>1.3005</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.9191</v>
+        <v>0.2796</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7333</v>
+        <v>-0.0184</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.1858</v>
+        <v>0.298</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6525</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7401</v>
+        <v>0.87</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5308</v>
+        <v>-0.289</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2572</v>
+        <v>-0.5047</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.788</v>
+        <v>0.2157</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1952</v>
+        <v>-1.13</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1952</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. GRELA ROJAS</t>
+          <t>R. ANDERSSON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7357</v>
+        <v>-0.9933</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1303</v>
+        <v>0.7682</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3946</v>
+        <v>-1.7615</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8532999999999999</v>
+        <v>-0.65</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7452</v>
+        <v>-0.4564</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5985</v>
+        <v>-0.1936</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5737</v>
+        <v>2.2691</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7268</v>
+        <v>0.2769</v>
       </c>
       <c r="L20" t="n">
-        <v>1.3005</v>
+        <v>1.9922</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2796</v>
+        <v>-2.9191</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0184</v>
+        <v>-0.7333</v>
       </c>
       <c r="O20" t="n">
-        <v>0.298</v>
+        <v>-2.1858</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.2175</v>
+        <v>0.6525</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R20" t="n">
-        <v>0.87</v>
+        <v>1.7401</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2415</v>
+        <v>-0.8006</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6165</v>
+        <v>-0.4134</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3749</v>
+        <v>-0.3873</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.13</v>
+        <v>-0.1952</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.13</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. QUINTELA SALVADOR</t>
+          <t>A. GALAN POZO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.7859</v>
+        <v>-3.1105</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9983</v>
+        <v>-1.7895</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7876</v>
+        <v>-1.321</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.9112</v>
+        <v>-2.6169</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.2107</v>
+        <v>-1.5117</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7004</v>
+        <v>-1.1052</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.2448</v>
+        <v>-1.8797</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.0098</v>
+        <v>-0.5808</v>
       </c>
       <c r="L21" t="n">
-        <v>0.765</v>
+        <v>-1.2989</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.6663</v>
+        <v>-0.7372</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2009</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.4654</v>
+        <v>0.1936</v>
       </c>
       <c r="P21" t="n">
-        <v>1.5225</v>
+        <v>1.0875</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5225</v>
+        <v>1.0875</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2673</v>
+        <v>-0.256</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7534999999999999</v>
+        <v>0.0901</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5138</v>
+        <v>-0.3461</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.13</v>
+        <v>-1.3252</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.13</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. GALAN POZO</t>
+          <t>S. QUINTELA SALVADOR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3771</v>
+        <v>-3.4018</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9071</v>
+        <v>-1.8865</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.47</v>
+        <v>-1.5153</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.6169</v>
+        <v>-2.9112</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.5117</v>
+        <v>-2.2107</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.1052</v>
+        <v>-0.7004</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.8797</v>
+        <v>-1.2448</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5808</v>
+        <v>-2.0098</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.2989</v>
+        <v>0.765</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7372</v>
+        <v>-1.6663</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9308999999999999</v>
+        <v>-0.2009</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1936</v>
+        <v>-1.4654</v>
       </c>
       <c r="P22" t="n">
-        <v>1.0875</v>
+        <v>1.5225</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.0875</v>
+        <v>1.5225</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.5225</v>
+        <v>-0.8832</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0274</v>
+        <v>-0.6417</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4951</v>
+        <v>-0.2415</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.3252</v>
+        <v>-1.13</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.3252</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.5226</v>
+        <v>-7.1238</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.1184</v>
+        <v>-5.5654</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4042</v>
+        <v>-1.5583</v>
       </c>
       <c r="G23" t="n">
         <v>-8.0573</v>
@@ -2248,13 +2248,13 @@
         <v>1.0875</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6423</v>
+        <v>0.0412</v>
       </c>
       <c r="T23" t="n">
-        <v>0.9337</v>
+        <v>0.4867</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2914</v>
+        <v>-0.4455</v>
       </c>
       <c r="V23" t="n">
         <v>-0.1952</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4898999999999996</v>
+        <v>0.2550999999999997</v>
       </c>
       <c r="E24" t="n">
         <v>12.7112</v>
       </c>
       <c r="F24" t="n">
-        <v>-13.2011</v>
+        <v>-12.456</v>
       </c>
       <c r="G24" t="n">
         <v>-5.363</v>
@@ -2296,7 +2296,7 @@
         <v>-9.610299999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>4.2473</v>
+        <v>4.247300000000002</v>
       </c>
       <c r="J24" t="n">
         <v>10.4165</v>
@@ -2314,7 +2314,7 @@
         <v>-8.153500000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>-7.6262</v>
+        <v>-7.626199999999999</v>
       </c>
       <c r="P24" t="n">
         <v>9.787599999999999</v>
@@ -2326,22 +2326,22 @@
         <v>14.1379</v>
       </c>
       <c r="S24" t="n">
-        <v>-4.914800000000001</v>
+        <v>-4.169700000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.6762</v>
+        <v>-1.6764</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.2387</v>
+        <v>-2.4936</v>
       </c>
       <c r="V24" t="n">
-        <v>4.718447854656915e-16</v>
+        <v>6.938893903907228e-16</v>
       </c>
       <c r="W24" t="n">
         <v>8.321</v>
       </c>
       <c r="X24" t="n">
-        <v>-8.3209</v>
+        <v>-8.320899999999998</v>
       </c>
     </row>
   </sheetData>
